--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_02C_2026.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_02C_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\báo cáo 1\2026_KHNV 5 năm\file mẫu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\báo cáo 1\2026_KHNV năm 2027\file mẫu\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -926,9 +926,66 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,63 +1000,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1299,17 +1299,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="K1" s="78" t="s">
+      <c r="K1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
       <c r="T1" s="43"/>
       <c r="U1" s="43"/>
       <c r="V1" s="43"/>
@@ -1323,15 +1323,14 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
       <c r="D3" s="4"/>
       <c r="E3" s="12"/>
-      <c r="G3" s="51" t="s">
+      <c r="H3" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="12"/>
       <c r="K3" s="39"/>
       <c r="L3" s="39"/>
       <c r="M3" s="39"/>
@@ -1346,15 +1345,14 @@
       <c r="V3" s="39"/>
     </row>
     <row r="4" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="4"/>
       <c r="E4" s="13"/>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="13"/>
       <c r="K4" s="40"/>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
@@ -1373,166 +1371,166 @@
       <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:22" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
       <c r="T6" s="41"/>
       <c r="U6" s="41"/>
       <c r="V6" s="41"/>
     </row>
     <row r="7" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K7" s="93" t="s">
+      <c r="K7" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="93"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69" t="s">
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="83" t="s">
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="84"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="83" t="s">
+      <c r="M8" s="83"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="84"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="84"/>
-      <c r="S8" s="85"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="84"/>
       <c r="T8" s="42"/>
       <c r="U8" s="42"/>
       <c r="V8" s="42"/>
     </row>
     <row r="9" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="75" t="s">
+      <c r="A9" s="93"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="91" t="s">
+      <c r="G9" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="92"/>
-      <c r="I9" s="88" t="s">
+      <c r="H9" s="72"/>
+      <c r="I9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="91" t="s">
+      <c r="J9" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="92"/>
-      <c r="L9" s="88" t="s">
+      <c r="K9" s="72"/>
+      <c r="L9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="91" t="s">
+      <c r="M9" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="N9" s="92"/>
-      <c r="O9" s="88" t="s">
+      <c r="N9" s="72"/>
+      <c r="O9" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="P9" s="91" t="s">
+      <c r="P9" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="Q9" s="92"/>
-      <c r="R9" s="91" t="s">
+      <c r="Q9" s="72"/>
+      <c r="R9" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="92"/>
+      <c r="S9" s="72"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
       <c r="V9" s="16"/>
     </row>
     <row r="10" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="74"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="82" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="82" t="s">
+      <c r="H10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="89"/>
-      <c r="J10" s="82" t="s">
+      <c r="I10" s="75"/>
+      <c r="J10" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="82" t="s">
+      <c r="K10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="89"/>
-      <c r="M10" s="86" t="s">
+      <c r="L10" s="75"/>
+      <c r="M10" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="86" t="s">
+      <c r="N10" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="O10" s="89"/>
-      <c r="P10" s="82" t="s">
+      <c r="O10" s="75"/>
+      <c r="P10" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="82" t="s">
+      <c r="Q10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="R10" s="82" t="s">
+      <c r="R10" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="S10" s="82" t="s">
+      <c r="S10" s="77" t="s">
         <v>17</v>
       </c>
       <c r="T10" s="17"/>
@@ -1540,25 +1538,25 @@
       <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="74"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="87"/>
-      <c r="N11" s="87"/>
-      <c r="O11" s="90"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="82"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="82"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="77"/>
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
       <c r="V11" s="16"/>
@@ -4939,28 +4937,28 @@
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
-      <c r="J69" s="81"/>
-      <c r="K69" s="81"/>
-      <c r="L69" s="81"/>
-      <c r="M69" s="81"/>
-      <c r="N69" s="81"/>
-      <c r="O69" s="81"/>
+      <c r="J69" s="69"/>
+      <c r="K69" s="69"/>
+      <c r="L69" s="69"/>
+      <c r="M69" s="69"/>
+      <c r="N69" s="69"/>
+      <c r="O69" s="69"/>
       <c r="P69" s="16"/>
       <c r="Q69" s="16"/>
     </row>
     <row r="70" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
       <c r="I70" s="17"/>
-      <c r="J70" s="80"/>
-      <c r="K70" s="80"/>
-      <c r="L70" s="80"/>
-      <c r="M70" s="80"/>
-      <c r="N70" s="80"/>
-      <c r="O70" s="80"/>
-      <c r="P70" s="80"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
+      <c r="M70" s="70"/>
+      <c r="N70" s="70"/>
+      <c r="O70" s="70"/>
+      <c r="P70" s="70"/>
       <c r="Q70" s="48"/>
       <c r="R70" s="48"/>
       <c r="S70" s="48"/>
@@ -4973,16 +4971,16 @@
     <row r="71" spans="1:24" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
       <c r="I71" s="16"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="80"/>
-      <c r="L71" s="80"/>
-      <c r="M71" s="80"/>
-      <c r="N71" s="80"/>
-      <c r="O71" s="80"/>
-      <c r="P71" s="80"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
+      <c r="M71" s="70"/>
+      <c r="N71" s="70"/>
+      <c r="O71" s="70"/>
+      <c r="P71" s="70"/>
       <c r="Q71" s="49"/>
       <c r="R71" s="49"/>
       <c r="S71" s="49"/>
@@ -4995,18 +4993,18 @@
     <row r="72" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="81"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="69"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="J72" s="81"/>
-      <c r="K72" s="81"/>
-      <c r="L72" s="81"/>
-      <c r="M72" s="81"/>
-      <c r="N72" s="81"/>
-      <c r="O72" s="81"/>
-      <c r="P72" s="81"/>
+      <c r="J72" s="69"/>
+      <c r="K72" s="69"/>
+      <c r="L72" s="69"/>
+      <c r="M72" s="69"/>
+      <c r="N72" s="69"/>
+      <c r="O72" s="69"/>
+      <c r="P72" s="69"/>
       <c r="Q72" s="47"/>
       <c r="R72" s="47"/>
       <c r="T72" s="47"/>
@@ -5020,6 +5018,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A6:S6"/>
+    <mergeCell ref="J70:P70"/>
+    <mergeCell ref="J69:O69"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F9:F11"/>
     <mergeCell ref="C72:D72"/>
     <mergeCell ref="J71:P71"/>
     <mergeCell ref="J72:P72"/>
@@ -5036,30 +5058,6 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="M10:M11"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A6:S6"/>
-    <mergeCell ref="J70:P70"/>
-    <mergeCell ref="J69:O69"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="33" orientation="portrait" r:id="rId1"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_02C_2026.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_02C_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\update TTBC\update 2026\2026_T6_20_KHNV2027\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\báo cáo 1\2026_KHNV năm 2027\file mẫu\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -364,7 +364,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;;@"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\-#,##0.00;;@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +464,11 @@
       <i/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -651,7 +656,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -715,9 +720,6 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="9" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -804,6 +806,40 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,42 +917,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -925,7 +925,42 @@
     <cellStyle name="Normal 5" xfId="2"/>
     <cellStyle name="Normal_1a. Mau bieu Ke hoach hoa  949 ngay 08-6-2004" xfId="1"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1237,7 +1272,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:W67"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1245,252 +1282,254 @@
     <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="77.5546875" style="1" customWidth="1"/>
     <col min="4" max="6" width="13.77734375" style="1" customWidth="1"/>
-    <col min="7" max="18" width="13.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9.109375" style="2"/>
+    <col min="7" max="17" width="13.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" style="2" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" style="2" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="9.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="J1" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
+      <c r="J1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
       <c r="S1" s="16"/>
       <c r="T1" s="16"/>
       <c r="U1" s="16"/>
     </row>
     <row r="2" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
     </row>
     <row r="3" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="55" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
     </row>
     <row r="4" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
       <c r="S4" s="13"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
     </row>
     <row r="6" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
     </row>
     <row r="7" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J7" s="79" t="s">
+      <c r="J7" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="79"/>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="79"/>
-      <c r="R7" s="79"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="89"/>
+      <c r="O7" s="89"/>
+      <c r="P7" s="89"/>
+      <c r="Q7" s="89"/>
+      <c r="R7" s="89"/>
     </row>
     <row r="8" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="67"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="77"/>
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
       <c r="U8" s="15"/>
     </row>
     <row r="9" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="75" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="73"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="70" t="s">
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="73"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="70" t="s">
+      <c r="I9" s="83"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="73"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="70" t="s">
+      <c r="L9" s="83"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="73"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="74"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="84"/>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
       <c r="U9" s="10"/>
     </row>
     <row r="10" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="64" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="71"/>
-      <c r="I10" s="64" t="s">
+      <c r="H10" s="81"/>
+      <c r="I10" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="64" t="s">
+      <c r="J10" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="K10" s="71"/>
-      <c r="L10" s="68" t="s">
+      <c r="K10" s="81"/>
+      <c r="L10" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="71"/>
-      <c r="O10" s="64" t="s">
+      <c r="N10" s="81"/>
+      <c r="O10" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="P10" s="64" t="s">
+      <c r="P10" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="Q10" s="64" t="s">
+      <c r="Q10" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="R10" s="64" t="s">
+      <c r="R10" s="74" t="s">
         <v>7</v>
       </c>
       <c r="S10" s="11"/>
@@ -1498,24 +1537,24 @@
       <c r="U10" s="11"/>
     </row>
     <row r="11" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="64"/>
-      <c r="Q11" s="64"/>
-      <c r="R11" s="64"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="74"/>
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
@@ -1536,10 +1575,10 @@
       <c r="E12" s="3">
         <v>5</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="47">
         <v>6</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="47">
         <v>7</v>
       </c>
       <c r="H12" s="3">
@@ -1577,20 +1616,20 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="46">
         <f>D14+D34</f>
         <v>0</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="46">
         <f>E14+E34</f>
         <v>0</v>
       </c>
@@ -1602,7 +1641,7 @@
         <f t="shared" ref="G13:G62" si="1">IF(OR(ISBLANK(F13), F13="",AND(D13=0,F13=0)), "", IF(AND(D13=0, F13&gt;0), 100, IF(AND(D13&gt;0, F13=0), 0, ROUND((F13/D13)*100, 3))))</f>
         <v/>
       </c>
-      <c r="H13" s="47">
+      <c r="H13" s="46">
         <f>H14+H34</f>
         <v>0</v>
       </c>
@@ -1614,7 +1653,7 @@
         <f t="shared" ref="J13:J62" si="3">IF(OR(ISBLANK(I13), I13="",AND(E13=0,I13=0)), "", IF(AND(E13=0, I13&gt;0), 100, IF(AND(E13&gt;0, I13=0), 0, ROUND((I13/E13)*100, 3))))</f>
         <v/>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="46">
         <f>K14+K34</f>
         <v>0</v>
       </c>
@@ -1626,7 +1665,7 @@
         <f t="shared" ref="M13:M62" si="5">IF(OR(ISBLANK(L13), L13="",AND(H13=0,L13=0)), "", IF(AND(H13=0, L13&gt;0), 100, IF(AND(H13&gt;0, L13=0), 0, ROUND((L13/H13)*100, 3))))</f>
         <v/>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="46">
         <f>N14+N34</f>
         <v>0</v>
       </c>
@@ -1648,20 +1687,20 @@
       </c>
     </row>
     <row r="14" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="46">
         <f t="shared" ref="D14:E14" si="10">SUM(D15:D33)-D19-D24-D28-D31</f>
         <v>0</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -1673,7 +1712,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="46">
         <f>SUM(H15:H33)-H19-H24-H28-H31</f>
         <v>0</v>
       </c>
@@ -1685,7 +1724,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="46">
         <f>SUM(K15:K33)-K19-K24-K28-K31</f>
         <v>0</v>
       </c>
@@ -1697,7 +1736,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="46">
         <f>SUM(N15:N33)-N19-N24-N28-N31</f>
         <v>0</v>
       </c>
@@ -1722,17 +1761,20 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30">
+      <c r="A15" s="29">
         <v>1</v>
       </c>
       <c r="B15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="80"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="63">
+        <f>S15-E35</f>
+        <v>0</v>
+      </c>
       <c r="F15" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1741,7 +1783,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H15" s="22"/>
+      <c r="H15" s="63">
+        <f>T15-H35</f>
+        <v>0</v>
+      </c>
       <c r="I15" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1750,7 +1795,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="63">
+        <f>U15-K35</f>
+        <v>0</v>
+      </c>
       <c r="L15" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1759,7 +1807,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="63">
+        <f>V15-N35</f>
+        <v>0</v>
+      </c>
       <c r="O15" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -1781,17 +1832,20 @@
       <c r="U15" s="2"/>
     </row>
     <row r="16" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="30">
+      <c r="A16" s="29">
         <v>2</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="82"/>
-      <c r="E16" s="81"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="63">
+        <f>S16-E36</f>
+        <v>0</v>
+      </c>
       <c r="F16" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1800,7 +1854,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H16" s="22"/>
+      <c r="H16" s="63">
+        <f t="shared" ref="H16:H18" si="11">T16-H36</f>
+        <v>0</v>
+      </c>
       <c r="I16" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1809,7 +1866,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K16" s="22"/>
+      <c r="K16" s="63">
+        <f>U16-K36</f>
+        <v>0</v>
+      </c>
       <c r="L16" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1818,7 +1878,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N16" s="22"/>
+      <c r="N16" s="63">
+        <f t="shared" ref="N16:N18" si="12">V16-N36</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -1840,17 +1903,20 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30">
+      <c r="A17" s="29">
         <v>3</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="82"/>
-      <c r="E17" s="81"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="63">
+        <f t="shared" ref="E17:E18" si="13">S17-E37</f>
+        <v>0</v>
+      </c>
       <c r="F17" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1859,7 +1925,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="63">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="I17" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1868,7 +1937,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="63">
+        <f>U17-K37</f>
+        <v>0</v>
+      </c>
       <c r="L17" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1877,7 +1949,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N17" s="22"/>
+      <c r="N17" s="63">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="O17" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -1899,17 +1974,20 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="30">
+      <c r="A18" s="29">
         <v>4</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="63">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="F18" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1918,7 +1996,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H18" s="23"/>
+      <c r="H18" s="63">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="I18" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -1927,7 +2008,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K18" s="23"/>
+      <c r="K18" s="63">
+        <f>U18-K38</f>
+        <v>0</v>
+      </c>
       <c r="L18" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1936,7 +2020,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N18" s="23"/>
+      <c r="N18" s="63">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="O18" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -1958,57 +2045,57 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="82"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="24" t="str">
+      <c r="D19" s="54"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="24" t="str">
+      <c r="G19" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H19" s="25"/>
-      <c r="I19" s="24" t="str">
+      <c r="H19" s="63"/>
+      <c r="I19" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J19" s="24" t="str">
+      <c r="J19" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="24" t="str">
+      <c r="K19" s="63"/>
+      <c r="L19" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M19" s="24" t="str">
+      <c r="M19" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N19" s="25"/>
-      <c r="O19" s="24" t="str">
+      <c r="N19" s="63"/>
+      <c r="O19" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P19" s="24" t="str">
+      <c r="P19" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q19" s="24" t="str">
+      <c r="Q19" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R19" s="24" t="str">
+      <c r="R19" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -2017,17 +2104,20 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30">
+      <c r="A20" s="29">
         <v>5</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="81"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="63">
+        <f>S20-E39</f>
+        <v>0</v>
+      </c>
       <c r="F20" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2036,7 +2126,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H20" s="22"/>
+      <c r="H20" s="63">
+        <f>T20-H39</f>
+        <v>0</v>
+      </c>
       <c r="I20" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2045,7 +2138,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K20" s="22"/>
+      <c r="K20" s="63">
+        <f>U20-K39</f>
+        <v>0</v>
+      </c>
       <c r="L20" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2054,7 +2150,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N20" s="22"/>
+      <c r="N20" s="63">
+        <f>V20-N39</f>
+        <v>0</v>
+      </c>
       <c r="O20" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2076,17 +2175,20 @@
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A21" s="30">
+      <c r="A21" s="29">
         <v>6</v>
       </c>
       <c r="B21" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="81"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="63">
+        <f>S21-E40</f>
+        <v>0</v>
+      </c>
       <c r="F21" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2095,7 +2197,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="63">
+        <f>T21-H40</f>
+        <v>0</v>
+      </c>
       <c r="I21" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2104,7 +2209,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="63">
+        <f>U21-K40</f>
+        <v>0</v>
+      </c>
       <c r="L21" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2113,7 +2221,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N21" s="22"/>
+      <c r="N21" s="63">
+        <f>V21-N40</f>
+        <v>0</v>
+      </c>
       <c r="O21" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2132,17 +2243,17 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="30">
+      <c r="A22" s="29">
         <v>7</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="82"/>
-      <c r="E22" s="81"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2151,7 +2262,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H22" s="22"/>
+      <c r="H22" s="63"/>
       <c r="I22" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2160,7 +2271,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="63"/>
       <c r="L22" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2169,7 +2280,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N22" s="22"/>
+      <c r="N22" s="63"/>
       <c r="O22" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2188,17 +2299,20 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A23" s="30">
+      <c r="A23" s="29">
         <v>8</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="82"/>
-      <c r="E23" s="81"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="63">
+        <f>S23-E41</f>
+        <v>0</v>
+      </c>
       <c r="F23" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2207,7 +2321,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H23" s="22"/>
+      <c r="H23" s="63">
+        <f>T23-H41</f>
+        <v>0</v>
+      </c>
       <c r="I23" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2216,7 +2333,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K23" s="22"/>
+      <c r="K23" s="63">
+        <f>U23-K41</f>
+        <v>0</v>
+      </c>
       <c r="L23" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2225,7 +2345,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N23" s="22"/>
+      <c r="N23" s="63">
+        <f>V23-N41</f>
+        <v>0</v>
+      </c>
       <c r="O23" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2244,57 +2367,57 @@
       </c>
     </row>
     <row r="24" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="82"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="24" t="str">
+      <c r="D24" s="54"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="24" t="str">
+      <c r="G24" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="24" t="str">
+      <c r="H24" s="63"/>
+      <c r="I24" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J24" s="24" t="str">
+      <c r="J24" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K24" s="25"/>
-      <c r="L24" s="24" t="str">
+      <c r="K24" s="63"/>
+      <c r="L24" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M24" s="24" t="str">
+      <c r="M24" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N24" s="25"/>
-      <c r="O24" s="24" t="str">
+      <c r="N24" s="63"/>
+      <c r="O24" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P24" s="24" t="str">
+      <c r="P24" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q24" s="24" t="str">
+      <c r="Q24" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R24" s="24" t="str">
+      <c r="R24" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -2303,17 +2426,20 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30">
+      <c r="A25" s="29">
         <v>9</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="82"/>
-      <c r="E25" s="81"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="63">
+        <f t="shared" ref="E25:E30" si="14">S25-E42</f>
+        <v>0</v>
+      </c>
       <c r="F25" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2322,7 +2448,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H25" s="22"/>
+      <c r="H25" s="63">
+        <f t="shared" ref="H25:H30" si="15">T25-H42</f>
+        <v>0</v>
+      </c>
       <c r="I25" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2331,7 +2460,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K25" s="22"/>
+      <c r="K25" s="63">
+        <f t="shared" ref="K25:K30" si="16">U25-K42</f>
+        <v>0</v>
+      </c>
       <c r="L25" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2340,7 +2472,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N25" s="22"/>
+      <c r="N25" s="63">
+        <f t="shared" ref="N25:N30" si="17">V25-N42</f>
+        <v>0</v>
+      </c>
       <c r="O25" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2362,17 +2497,20 @@
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="30">
+      <c r="A26" s="29">
         <v>10</v>
       </c>
       <c r="B26" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="82"/>
-      <c r="E26" s="81"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="63">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="F26" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2381,7 +2519,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H26" s="22"/>
+      <c r="H26" s="63">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="I26" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2390,7 +2531,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K26" s="22"/>
+      <c r="K26" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="L26" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2399,7 +2543,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N26" s="22"/>
+      <c r="N26" s="63">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="O26" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2418,17 +2565,20 @@
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A27" s="30">
+      <c r="A27" s="29">
         <v>11</v>
       </c>
       <c r="B27" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="82"/>
-      <c r="E27" s="81"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="63">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="F27" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2437,7 +2587,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H27" s="22"/>
+      <c r="H27" s="63">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="I27" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2446,7 +2599,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K27" s="22"/>
+      <c r="K27" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="L27" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2455,7 +2611,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N27" s="22"/>
+      <c r="N27" s="63">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="O27" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2474,17 +2633,20 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="31" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="82"/>
-      <c r="E28" s="81"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="63">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="F28" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2493,7 +2655,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H28" s="22"/>
+      <c r="H28" s="63">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="I28" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2502,7 +2667,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K28" s="22"/>
+      <c r="K28" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="L28" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2511,7 +2679,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N28" s="22"/>
+      <c r="N28" s="63">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="O28" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2530,17 +2701,20 @@
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="30">
+      <c r="A29" s="29">
         <v>12</v>
       </c>
       <c r="B29" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="82"/>
-      <c r="E29" s="81"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="63">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="F29" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2549,7 +2723,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H29" s="22"/>
+      <c r="H29" s="63">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="I29" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2558,7 +2735,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K29" s="22"/>
+      <c r="K29" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="L29" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2567,7 +2747,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N29" s="22"/>
+      <c r="N29" s="63">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="O29" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2586,17 +2769,20 @@
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="30">
+      <c r="A30" s="29">
         <v>13</v>
       </c>
       <c r="B30" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="82"/>
-      <c r="E30" s="81"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="63">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="F30" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2605,7 +2791,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H30" s="22"/>
+      <c r="H30" s="63">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="I30" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2614,7 +2803,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K30" s="22"/>
+      <c r="K30" s="63">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="L30" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2623,7 +2815,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N30" s="22"/>
+      <c r="N30" s="63">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="O30" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2642,73 +2837,73 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B31" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="82"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="24" t="str">
+      <c r="D31" s="54"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="24" t="str">
+      <c r="G31" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H31" s="25"/>
-      <c r="I31" s="24" t="str">
+      <c r="H31" s="63"/>
+      <c r="I31" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J31" s="24" t="str">
+      <c r="J31" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K31" s="25"/>
-      <c r="L31" s="24" t="str">
+      <c r="K31" s="63"/>
+      <c r="L31" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M31" s="24" t="str">
+      <c r="M31" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N31" s="25"/>
-      <c r="O31" s="24" t="str">
+      <c r="N31" s="63"/>
+      <c r="O31" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P31" s="24" t="str">
+      <c r="P31" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q31" s="24" t="str">
+      <c r="Q31" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R31" s="24" t="str">
+      <c r="R31" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A32" s="30">
+      <c r="A32" s="29">
         <v>14</v>
       </c>
       <c r="B32" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="82"/>
-      <c r="E32" s="81"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="63"/>
       <c r="F32" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2717,7 +2912,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H32" s="22"/>
+      <c r="H32" s="63"/>
       <c r="I32" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2726,7 +2921,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K32" s="22"/>
+      <c r="K32" s="63"/>
       <c r="L32" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2735,7 +2930,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N32" s="22"/>
+      <c r="N32" s="63"/>
       <c r="O32" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2754,17 +2949,20 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A33" s="30">
+      <c r="A33" s="29">
         <v>15</v>
       </c>
       <c r="B33" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="82"/>
-      <c r="E33" s="81"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="63">
+        <f>S33</f>
+        <v>0</v>
+      </c>
       <c r="F33" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2773,7 +2971,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H33" s="22"/>
+      <c r="H33" s="63">
+        <f>T33</f>
+        <v>0</v>
+      </c>
       <c r="I33" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2782,7 +2983,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K33" s="22"/>
+      <c r="K33" s="63">
+        <f>U33</f>
+        <v>0</v>
+      </c>
       <c r="L33" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2791,7 +2995,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N33" s="22"/>
+      <c r="N33" s="63">
+        <f>V33</f>
+        <v>0</v>
+      </c>
       <c r="O33" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2810,21 +3017,21 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>17</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="47">
-        <f t="shared" ref="D34:E34" si="11">SUM(D35:D48)-D45</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="47">
-        <f t="shared" si="11"/>
+      <c r="D34" s="46">
+        <f t="shared" ref="D34:E34" si="18">SUM(D35:D48)-D45</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="46">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F34" s="20" t="str">
@@ -2835,8 +3042,8 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H34" s="47">
-        <f t="shared" ref="H34" si="12">SUM(H35:H48)-H45</f>
+      <c r="H34" s="46">
+        <f t="shared" ref="H34" si="19">SUM(H35:H48)-H45</f>
         <v>0</v>
       </c>
       <c r="I34" s="20" t="str">
@@ -2847,8 +3054,8 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K34" s="47">
-        <f t="shared" ref="K34" si="13">SUM(K35:K48)-K45</f>
+      <c r="K34" s="46">
+        <f t="shared" ref="K34" si="20">SUM(K35:K48)-K45</f>
         <v>0</v>
       </c>
       <c r="L34" s="20" t="str">
@@ -2859,8 +3066,8 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N34" s="47">
-        <f t="shared" ref="N34" si="14">SUM(N35:N48)-N45</f>
+      <c r="N34" s="46">
+        <f t="shared" ref="N34" si="21">SUM(N35:N48)-N45</f>
         <v>0</v>
       </c>
       <c r="O34" s="20" t="str">
@@ -2881,17 +3088,17 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A35" s="30">
+      <c r="A35" s="29">
         <v>1</v>
       </c>
       <c r="B35" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="35" t="s">
         <v>23</v>
       </c>
       <c r="D35" s="21"/>
-      <c r="E35" s="81"/>
+      <c r="E35" s="53"/>
       <c r="F35" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2937,17 +3144,17 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A36" s="30">
+      <c r="A36" s="29">
         <v>2</v>
       </c>
       <c r="B36" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="36" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="21"/>
-      <c r="E36" s="81"/>
+      <c r="E36" s="53"/>
       <c r="F36" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2993,17 +3200,17 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A37" s="30">
+      <c r="A37" s="29">
         <v>3</v>
       </c>
       <c r="B37" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="37" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="21"/>
-      <c r="E37" s="81"/>
+      <c r="E37" s="53"/>
       <c r="F37" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3049,17 +3256,17 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A38" s="30">
+      <c r="A38" s="29">
         <v>4</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="37" t="s">
         <v>26</v>
       </c>
       <c r="D38" s="21"/>
-      <c r="E38" s="81"/>
+      <c r="E38" s="53"/>
       <c r="F38" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3105,17 +3312,17 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A39" s="30">
+      <c r="A39" s="29">
         <v>5</v>
       </c>
       <c r="B39" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="39" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="21"/>
-      <c r="E39" s="81"/>
+      <c r="E39" s="53"/>
       <c r="F39" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3161,17 +3368,17 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A40" s="30">
+      <c r="A40" s="29">
         <v>6</v>
       </c>
       <c r="B40" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="37" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="21"/>
-      <c r="E40" s="81"/>
+      <c r="E40" s="53"/>
       <c r="F40" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3217,17 +3424,17 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A41" s="30">
+      <c r="A41" s="29">
         <v>7</v>
       </c>
       <c r="B41" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="37" t="s">
         <v>31</v>
       </c>
       <c r="D41" s="21"/>
-      <c r="E41" s="81"/>
+      <c r="E41" s="53"/>
       <c r="F41" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3273,17 +3480,17 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A42" s="30">
+      <c r="A42" s="29">
         <v>8</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="37" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="21"/>
-      <c r="E42" s="81"/>
+      <c r="E42" s="53"/>
       <c r="F42" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3329,17 +3536,17 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A43" s="30">
+      <c r="A43" s="29">
         <v>9</v>
       </c>
       <c r="B43" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="37" t="s">
         <v>33</v>
       </c>
       <c r="D43" s="21"/>
-      <c r="E43" s="81"/>
+      <c r="E43" s="53"/>
       <c r="F43" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3385,17 +3592,17 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A44" s="30">
+      <c r="A44" s="29">
         <v>10</v>
       </c>
       <c r="B44" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="39" t="s">
         <v>34</v>
       </c>
       <c r="D44" s="21"/>
-      <c r="E44" s="81"/>
+      <c r="E44" s="53"/>
       <c r="F44" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3441,73 +3648,73 @@
       </c>
     </row>
     <row r="45" spans="1:22" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B45" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D45" s="84"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="24" t="str">
+      <c r="D45" s="55"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G45" s="24" t="str">
+      <c r="G45" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H45" s="25"/>
-      <c r="I45" s="24" t="str">
+      <c r="H45" s="24"/>
+      <c r="I45" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J45" s="24" t="str">
+      <c r="J45" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K45" s="25"/>
-      <c r="L45" s="24" t="str">
+      <c r="K45" s="24"/>
+      <c r="L45" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M45" s="24" t="str">
+      <c r="M45" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N45" s="25"/>
-      <c r="O45" s="24" t="str">
+      <c r="N45" s="24"/>
+      <c r="O45" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P45" s="24" t="str">
+      <c r="P45" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q45" s="24" t="str">
+      <c r="Q45" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R45" s="24" t="str">
+      <c r="R45" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="33">
+      <c r="A46" s="32">
         <v>11</v>
       </c>
       <c r="B46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="41" t="s">
         <v>36</v>
       </c>
       <c r="D46" s="21"/>
-      <c r="E46" s="81"/>
+      <c r="E46" s="53"/>
       <c r="F46" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3557,17 +3764,17 @@
       <c r="V46" s="2"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A47" s="30">
+      <c r="A47" s="29">
         <v>12</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="39" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="21"/>
-      <c r="E47" s="81"/>
+      <c r="E47" s="53"/>
       <c r="F47" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3613,17 +3820,20 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A48" s="30">
+      <c r="A48" s="29">
         <v>13</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="21"/>
-      <c r="E48" s="81"/>
+      <c r="E48" s="63">
+        <f>S48</f>
+        <v>0</v>
+      </c>
       <c r="F48" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3632,7 +3842,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="22"/>
+      <c r="H48" s="63">
+        <f>T48</f>
+        <v>0</v>
+      </c>
       <c r="I48" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3641,7 +3854,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K48" s="22"/>
+      <c r="K48" s="63">
+        <f>U48</f>
+        <v>0</v>
+      </c>
       <c r="L48" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3650,7 +3866,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N48" s="22"/>
+      <c r="N48" s="63">
+        <f>V48</f>
+        <v>0</v>
+      </c>
       <c r="O48" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3669,17 +3888,17 @@
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="27" t="s">
         <v>19</v>
       </c>
       <c r="B49" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="47"/>
-      <c r="E49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="45"/>
       <c r="F49" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3688,7 +3907,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="46"/>
+      <c r="H49" s="45"/>
       <c r="I49" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3697,7 +3916,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K49" s="46"/>
+      <c r="K49" s="45"/>
       <c r="L49" s="20" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -3706,7 +3925,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N49" s="46"/>
+      <c r="N49" s="45"/>
       <c r="O49" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3725,17 +3944,17 @@
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A50" s="30">
+      <c r="A50" s="29">
         <v>1</v>
       </c>
       <c r="B50" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="37" t="s">
         <v>43</v>
       </c>
       <c r="D50" s="21"/>
-      <c r="E50" s="81"/>
+      <c r="E50" s="53"/>
       <c r="F50" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3781,17 +4000,17 @@
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="30">
+      <c r="A51" s="29">
         <v>2</v>
       </c>
       <c r="B51" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="38" t="s">
+      <c r="C51" s="37" t="s">
         <v>44</v>
       </c>
       <c r="D51" s="21"/>
-      <c r="E51" s="81"/>
+      <c r="E51" s="53"/>
       <c r="F51" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3837,73 +4056,73 @@
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B52" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="32" t="s">
+      <c r="C52" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="84"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="24" t="str">
+      <c r="D52" s="55"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G52" s="24" t="str">
+      <c r="G52" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="25"/>
-      <c r="I52" s="24" t="str">
+      <c r="H52" s="24"/>
+      <c r="I52" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J52" s="24" t="str">
+      <c r="J52" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K52" s="25"/>
-      <c r="L52" s="24" t="str">
+      <c r="K52" s="24"/>
+      <c r="L52" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M52" s="24" t="str">
+      <c r="M52" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N52" s="25"/>
-      <c r="O52" s="24" t="str">
+      <c r="N52" s="24"/>
+      <c r="O52" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P52" s="24" t="str">
+      <c r="P52" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q52" s="24" t="str">
+      <c r="Q52" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R52" s="24" t="str">
+      <c r="R52" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="30">
+      <c r="A53" s="29">
         <v>3</v>
       </c>
       <c r="B53" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="37" t="s">
         <v>46</v>
       </c>
       <c r="D53" s="21"/>
-      <c r="E53" s="81"/>
+      <c r="E53" s="53"/>
       <c r="F53" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3952,57 +4171,57 @@
       <c r="U53" s="2"/>
     </row>
     <row r="54" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="32" t="s">
+      <c r="C54" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="84"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="24" t="str">
+      <c r="D54" s="55"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G54" s="24" t="str">
+      <c r="G54" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H54" s="25"/>
-      <c r="I54" s="24" t="str">
+      <c r="H54" s="24"/>
+      <c r="I54" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J54" s="24" t="str">
+      <c r="J54" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K54" s="25"/>
-      <c r="L54" s="24" t="str">
+      <c r="K54" s="24"/>
+      <c r="L54" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M54" s="24" t="str">
+      <c r="M54" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N54" s="25"/>
-      <c r="O54" s="24" t="str">
+      <c r="N54" s="24"/>
+      <c r="O54" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P54" s="24" t="str">
+      <c r="P54" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q54" s="24" t="str">
+      <c r="Q54" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R54" s="24" t="str">
+      <c r="R54" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4011,17 +4230,17 @@
       <c r="U54" s="2"/>
     </row>
     <row r="55" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="30">
+      <c r="A55" s="29">
         <v>4</v>
       </c>
       <c r="B55" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="38" t="s">
+      <c r="C55" s="37" t="s">
         <v>48</v>
       </c>
       <c r="D55" s="21"/>
-      <c r="E55" s="81"/>
+      <c r="E55" s="53"/>
       <c r="F55" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4070,57 +4289,57 @@
       <c r="U55" s="2"/>
     </row>
     <row r="56" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="32" t="s">
+      <c r="C56" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D56" s="84"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="24" t="str">
+      <c r="D56" s="55"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G56" s="24" t="str">
+      <c r="G56" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H56" s="25"/>
-      <c r="I56" s="24" t="str">
+      <c r="H56" s="24"/>
+      <c r="I56" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J56" s="24" t="str">
+      <c r="J56" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K56" s="25"/>
-      <c r="L56" s="24" t="str">
+      <c r="K56" s="24"/>
+      <c r="L56" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M56" s="24" t="str">
+      <c r="M56" s="23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N56" s="25"/>
-      <c r="O56" s="24" t="str">
+      <c r="N56" s="24"/>
+      <c r="O56" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P56" s="24" t="str">
+      <c r="P56" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q56" s="24" t="str">
+      <c r="Q56" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="R56" s="24" t="str">
+      <c r="R56" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4129,75 +4348,75 @@
       <c r="U56" s="2"/>
     </row>
     <row r="57" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="30">
+      <c r="A57" s="29">
         <v>5</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="87"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="87"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="87"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-      <c r="R57" s="86"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="58"/>
+      <c r="L57" s="57"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+      <c r="O57" s="57"/>
+      <c r="P57" s="57"/>
+      <c r="Q57" s="57"/>
+      <c r="R57" s="57"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
     </row>
     <row r="58" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B58" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C58" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="85"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
-      <c r="H58" s="87"/>
-      <c r="I58" s="86"/>
-      <c r="J58" s="86"/>
-      <c r="K58" s="87"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="86"/>
-      <c r="N58" s="87"/>
-      <c r="O58" s="86"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-      <c r="R58" s="86"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="58"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="57"/>
+      <c r="P58" s="57"/>
+      <c r="Q58" s="57"/>
+      <c r="R58" s="57"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
     </row>
     <row r="59" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="30">
+      <c r="A59" s="29">
         <v>6</v>
       </c>
       <c r="B59" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="38" t="s">
+      <c r="C59" s="37" t="s">
         <v>97</v>
       </c>
       <c r="D59" s="21"/>
-      <c r="E59" s="81"/>
+      <c r="E59" s="53"/>
       <c r="F59" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4246,17 +4465,17 @@
       <c r="U59" s="2"/>
     </row>
     <row r="60" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="30">
+      <c r="A60" s="29">
         <v>7</v>
       </c>
       <c r="B60" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="38" t="s">
+      <c r="C60" s="37" t="s">
         <v>98</v>
       </c>
       <c r="D60" s="21"/>
-      <c r="E60" s="81"/>
+      <c r="E60" s="53"/>
       <c r="F60" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4305,17 +4524,17 @@
       <c r="U60" s="2"/>
     </row>
     <row r="61" spans="1:21" s="4" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="30">
+      <c r="A61" s="29">
         <v>8</v>
       </c>
       <c r="B61" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="38" t="s">
+      <c r="C61" s="37" t="s">
         <v>50</v>
       </c>
       <c r="D61" s="21"/>
-      <c r="E61" s="81"/>
+      <c r="E61" s="53"/>
       <c r="F61" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4364,17 +4583,17 @@
       <c r="U61" s="2"/>
     </row>
     <row r="62" spans="1:21" s="4" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="45">
+      <c r="A62" s="44">
         <v>9</v>
       </c>
-      <c r="B62" s="45" t="s">
+      <c r="B62" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="44" t="s">
+      <c r="C62" s="43" t="s">
         <v>51</v>
       </c>
       <c r="D62" s="21"/>
-      <c r="E62" s="81"/>
+      <c r="E62" s="53"/>
       <c r="F62" s="20" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4422,47 +4641,47 @@
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A63" s="34" t="s">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="B63" s="53" t="s">
+      <c r="B63" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="D63" s="88"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="90" t="str">
-        <f t="shared" ref="F14:F63" si="15">IF(OR(D63&lt;&gt;0,E63&lt;&gt;0),E63-D63,"")</f>
-        <v/>
-      </c>
-      <c r="G63" s="90" t="str">
-        <f t="shared" ref="G14:G63" si="16">IF(OR(ISBLANK(F63), F63="",AND(D63=0,F63=0)), "", IF(AND(D63=0, F63&gt;0), 100, IF(AND(D63&gt;0, F63=0), 0, ROUND((F63/D63)*100, 3))))</f>
-        <v/>
-      </c>
-      <c r="H63" s="91"/>
-      <c r="I63" s="90"/>
-      <c r="J63" s="90"/>
-      <c r="K63" s="91"/>
-      <c r="L63" s="90"/>
-      <c r="M63" s="90"/>
-      <c r="N63" s="91"/>
-      <c r="O63" s="90" t="str">
-        <f t="shared" ref="O63" si="17">IF(OR(K63&lt;&gt;0,N63&lt;&gt;0),N63-K63,"")</f>
-        <v/>
-      </c>
-      <c r="P63" s="90" t="str">
-        <f t="shared" ref="P63" si="18">IF(OR(ISBLANK(O63), O63="",AND(K63=0,O63=0)), "", IF(AND(K63=0, O63&gt;0), 100, IF(AND(K63&gt;0, O63=0), 0, ROUND((O63/K63)*100, 3))))</f>
-        <v/>
-      </c>
-      <c r="Q63" s="90" t="str">
-        <f t="shared" ref="Q63" si="19">IF(OR(N63&lt;&gt;0,D63&lt;&gt;0),N63-D63,"")</f>
-        <v/>
-      </c>
-      <c r="R63" s="90" t="str">
-        <f t="shared" ref="R63" si="20">IF(OR(ISBLANK(Q63), Q63="",AND(D63=0,Q63=0)), "", IF(AND(D63=0, Q63&gt;0), 100, IF(AND(D63&gt;0, Q63=0), 0, ROUND((Q63/D63)*100, 3))))</f>
+      <c r="D63" s="59"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="61" t="str">
+        <f t="shared" ref="F63" si="22">IF(OR(D63&lt;&gt;0,E63&lt;&gt;0),E63-D63,"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="61" t="str">
+        <f t="shared" ref="G63" si="23">IF(OR(ISBLANK(F63), F63="",AND(D63=0,F63=0)), "", IF(AND(D63=0, F63&gt;0), 100, IF(AND(D63&gt;0, F63=0), 0, ROUND((F63/D63)*100, 3))))</f>
+        <v/>
+      </c>
+      <c r="H63" s="62"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="62"/>
+      <c r="L63" s="61"/>
+      <c r="M63" s="61"/>
+      <c r="N63" s="62"/>
+      <c r="O63" s="61" t="str">
+        <f t="shared" ref="O63" si="24">IF(OR(K63&lt;&gt;0,N63&lt;&gt;0),N63-K63,"")</f>
+        <v/>
+      </c>
+      <c r="P63" s="61" t="str">
+        <f t="shared" ref="P63" si="25">IF(OR(ISBLANK(O63), O63="",AND(K63=0,O63=0)), "", IF(AND(K63=0, O63&gt;0), 100, IF(AND(K63&gt;0, O63=0), 0, ROUND((O63/K63)*100, 3))))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="61" t="str">
+        <f t="shared" ref="Q63" si="26">IF(OR(N63&lt;&gt;0,D63&lt;&gt;0),N63-D63,"")</f>
+        <v/>
+      </c>
+      <c r="R63" s="61" t="str">
+        <f t="shared" ref="R63" si="27">IF(OR(ISBLANK(Q63), Q63="",AND(D63=0,Q63=0)), "", IF(AND(D63=0, Q63&gt;0), 100, IF(AND(D63&gt;0, Q63=0), 0, ROUND((Q63/D63)*100, 3))))</f>
         <v/>
       </c>
     </row>
@@ -4489,15 +4708,15 @@
     <row r="65" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
-      <c r="C65" s="27"/>
+      <c r="C65" s="26"/>
       <c r="H65" s="11"/>
-      <c r="I65" s="63"/>
-      <c r="J65" s="63"/>
-      <c r="K65" s="63"/>
-      <c r="L65" s="63"/>
-      <c r="M65" s="63"/>
-      <c r="N65" s="63"/>
-      <c r="O65" s="63"/>
+      <c r="I65" s="73"/>
+      <c r="J65" s="73"/>
+      <c r="K65" s="73"/>
+      <c r="L65" s="73"/>
+      <c r="M65" s="73"/>
+      <c r="N65" s="73"/>
+      <c r="O65" s="73"/>
       <c r="P65" s="18"/>
       <c r="Q65" s="18"/>
       <c r="R65" s="18"/>
@@ -4510,15 +4729,15 @@
     <row r="66" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
-      <c r="C66" s="27"/>
+      <c r="C66" s="26"/>
       <c r="H66" s="10"/>
-      <c r="I66" s="63"/>
-      <c r="J66" s="63"/>
-      <c r="K66" s="63"/>
-      <c r="L66" s="63"/>
-      <c r="M66" s="63"/>
-      <c r="N66" s="63"/>
-      <c r="O66" s="63"/>
+      <c r="I66" s="73"/>
+      <c r="J66" s="73"/>
+      <c r="K66" s="73"/>
+      <c r="L66" s="73"/>
+      <c r="M66" s="73"/>
+      <c r="N66" s="73"/>
+      <c r="O66" s="73"/>
       <c r="P66" s="19"/>
       <c r="Q66" s="19"/>
       <c r="R66" s="19"/>
@@ -4531,17 +4750,17 @@
     <row r="67" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="26"/>
+      <c r="C67" s="25"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
-      <c r="I67" s="78"/>
-      <c r="J67" s="78"/>
-      <c r="K67" s="78"/>
-      <c r="L67" s="78"/>
-      <c r="M67" s="78"/>
-      <c r="N67" s="78"/>
-      <c r="O67" s="78"/>
+      <c r="I67" s="88"/>
+      <c r="J67" s="88"/>
+      <c r="K67" s="88"/>
+      <c r="L67" s="88"/>
+      <c r="M67" s="88"/>
+      <c r="N67" s="88"/>
+      <c r="O67" s="88"/>
       <c r="P67" s="17"/>
       <c r="Q67" s="17"/>
       <c r="S67" s="17"/>
@@ -4591,31 +4810,31 @@
     <mergeCell ref="E8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="H13">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$H$13 &lt;&gt;$H$63</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$K$13&lt;&gt;$K$63</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$N$13&lt;&gt;$N$63</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>$E$13&lt;&gt;$E$63</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D13">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$D$13&lt;&gt;$D$63</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>$E$13&lt;&gt;$E$63</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="33" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="44" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>